--- a/ERP/uploads/imports/clients_template.xlsx
+++ b/ERP/uploads/imports/clients_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -70,7 +70,13 @@
     <t xml:space="preserve">Notas adicionales</t>
   </si>
   <si>
-    <t xml:space="preserve">21123@gmail.com</t>
+    <t xml:space="preserve">Juan Pérez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innova Arte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Quito</t>
@@ -80,6 +86,24 @@
   </si>
   <si>
     <t xml:space="preserve">Cliente frecuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Pincay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mankar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prueba</t>
   </si>
 </sst>
 </file>
@@ -89,7 +113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +142,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -188,7 +220,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -444,7 +476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -509,32 +541,65 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>321123</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>1323</v>
+      <c r="A3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>17</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>1231231</v>
+        <v>1723456789</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>12412412</v>
+        <v>1999999999</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>19</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>19</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>1308386000</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>9594275677</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" display="Juan@gmail.com"/>
+    <hyperlink ref="E4" r:id="rId2" display="Manuel@hotmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
